--- a/inventory-backend/assets/inventory_template.xlsx
+++ b/inventory-backend/assets/inventory_template.xlsx
@@ -32,9 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -398,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="45.83203125" customWidth="1"/>
@@ -605,9 +604,56 @@
         <v>24011719</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>20154001</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MATERIAL IN TRANSFER</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Y013</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v>KG</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>500</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>365</v>
+      </c>
+      <c r="M5">
+        <v>1735689600</v>
+      </c>
+      <c r="N5">
+        <v>1704067200</v>
+      </c>
+      <c r="O5" t="str">
+        <v>24011720</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
   </ignoredErrors>
 </worksheet>
 </file>